--- a/network_excel_transformer/output/2G3G4G_Cell Info_CELLS_2G.xlsx
+++ b/network_excel_transformer/output/2G3G4G_Cell Info_CELLS_2G.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -438,6 +438,8 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +470,16 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Cell CI</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Freq. Band</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>azimuth</t>
         </is>
       </c>
@@ -495,6 +507,14 @@
         <v>43</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -521,6 +541,14 @@
         <v>41</v>
       </c>
       <c r="F3" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -547,6 +575,14 @@
         <v>74</v>
       </c>
       <c r="F4" s="2" t="n">
+        <v>45942</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -573,6 +609,14 @@
         <v>43</v>
       </c>
       <c r="F5" s="2" t="n">
+        <v>49390</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -599,6 +643,14 @@
         <v>68</v>
       </c>
       <c r="F6" s="2" t="n">
+        <v>49391</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -625,6 +677,14 @@
         <v>34</v>
       </c>
       <c r="F7" s="2" t="n">
+        <v>49392</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -651,6 +711,14 @@
         <v>68</v>
       </c>
       <c r="F8" s="2" t="n">
+        <v>49640</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -677,6 +745,14 @@
         <v>26</v>
       </c>
       <c r="F9" s="2" t="n">
+        <v>49641</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -703,6 +779,14 @@
         <v>44</v>
       </c>
       <c r="F10" s="2" t="n">
+        <v>49642</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -729,6 +813,14 @@
         <v>29</v>
       </c>
       <c r="F11" s="2" t="n">
+        <v>49740</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -755,6 +847,14 @@
         <v>43</v>
       </c>
       <c r="F12" s="2" t="n">
+        <v>49741</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -781,6 +881,14 @@
         <v>28</v>
       </c>
       <c r="F13" s="2" t="n">
+        <v>49742</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -807,6 +915,14 @@
         <v>28</v>
       </c>
       <c r="F14" s="2" t="n">
+        <v>49780</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,6 +949,14 @@
         <v>42</v>
       </c>
       <c r="F15" s="2" t="n">
+        <v>49781</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -859,6 +983,14 @@
         <v>32</v>
       </c>
       <c r="F16" s="2" t="n">
+        <v>49782</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -885,6 +1017,14 @@
         <v>29</v>
       </c>
       <c r="F17" s="2" t="n">
+        <v>49830</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -911,6 +1051,14 @@
         <v>44</v>
       </c>
       <c r="F18" s="2" t="n">
+        <v>49831</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -937,6 +1085,14 @@
         <v>72</v>
       </c>
       <c r="F19" s="2" t="n">
+        <v>49832</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -963,6 +1119,14 @@
         <v>40</v>
       </c>
       <c r="F20" s="2" t="n">
+        <v>49840</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -989,6 +1153,14 @@
         <v>42</v>
       </c>
       <c r="F21" s="2" t="n">
+        <v>49841</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1015,6 +1187,14 @@
         <v>44</v>
       </c>
       <c r="F22" s="2" t="n">
+        <v>49842</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1041,6 +1221,14 @@
         <v>30</v>
       </c>
       <c r="F23" s="2" t="n">
+        <v>49850</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1067,6 +1255,14 @@
         <v>68</v>
       </c>
       <c r="F24" s="2" t="n">
+        <v>49851</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1093,6 +1289,14 @@
         <v>44</v>
       </c>
       <c r="F25" s="2" t="n">
+        <v>49852</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1119,6 +1323,14 @@
         <v>31</v>
       </c>
       <c r="F26" s="2" t="n">
+        <v>50180</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1145,6 +1357,14 @@
         <v>68</v>
       </c>
       <c r="F27" s="2" t="n">
+        <v>50181</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1171,6 +1391,14 @@
         <v>43</v>
       </c>
       <c r="F28" s="2" t="n">
+        <v>50182</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1197,6 +1425,14 @@
         <v>42</v>
       </c>
       <c r="F29" s="2" t="n">
+        <v>50200</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1223,6 +1459,14 @@
         <v>29</v>
       </c>
       <c r="F30" s="2" t="n">
+        <v>50201</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1249,6 +1493,14 @@
         <v>37</v>
       </c>
       <c r="F31" s="2" t="n">
+        <v>50202</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1275,6 +1527,14 @@
         <v>42</v>
       </c>
       <c r="F32" s="2" t="n">
+        <v>50210</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1301,6 +1561,14 @@
         <v>30</v>
       </c>
       <c r="F33" s="2" t="n">
+        <v>50211</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1327,6 +1595,14 @@
         <v>30</v>
       </c>
       <c r="F34" s="2" t="n">
+        <v>50212</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1353,6 +1629,14 @@
         <v>44</v>
       </c>
       <c r="F35" s="2" t="n">
+        <v>50290</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1379,6 +1663,14 @@
         <v>70</v>
       </c>
       <c r="F36" s="2" t="n">
+        <v>50291</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1405,6 +1697,14 @@
         <v>26</v>
       </c>
       <c r="F37" s="2" t="n">
+        <v>50292</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1431,6 +1731,14 @@
         <v>68</v>
       </c>
       <c r="F38" s="2" t="n">
+        <v>50360</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1457,6 +1765,14 @@
         <v>66</v>
       </c>
       <c r="F39" s="2" t="n">
+        <v>50361</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1483,6 +1799,14 @@
         <v>35</v>
       </c>
       <c r="F40" s="2" t="n">
+        <v>50362</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1509,6 +1833,14 @@
         <v>26</v>
       </c>
       <c r="F41" s="2" t="n">
+        <v>50380</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1535,6 +1867,14 @@
         <v>42</v>
       </c>
       <c r="F42" s="2" t="n">
+        <v>50381</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1561,6 +1901,14 @@
         <v>44</v>
       </c>
       <c r="F43" s="2" t="n">
+        <v>50382</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1587,6 +1935,14 @@
         <v>26</v>
       </c>
       <c r="F44" s="2" t="n">
+        <v>50420</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1613,6 +1969,14 @@
         <v>43</v>
       </c>
       <c r="F45" s="2" t="n">
+        <v>50421</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1639,6 +2003,14 @@
         <v>37</v>
       </c>
       <c r="F46" s="2" t="n">
+        <v>50422</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1665,6 +2037,14 @@
         <v>35</v>
       </c>
       <c r="F47" s="2" t="n">
+        <v>50430</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1691,6 +2071,14 @@
         <v>42</v>
       </c>
       <c r="F48" s="2" t="n">
+        <v>50431</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1717,6 +2105,14 @@
         <v>72</v>
       </c>
       <c r="F49" s="2" t="n">
+        <v>50432</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1743,6 +2139,14 @@
         <v>39</v>
       </c>
       <c r="F50" s="2" t="n">
+        <v>50440</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1769,6 +2173,14 @@
         <v>43</v>
       </c>
       <c r="F51" s="2" t="n">
+        <v>50441</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1795,6 +2207,14 @@
         <v>31</v>
       </c>
       <c r="F52" s="2" t="n">
+        <v>50442</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1821,6 +2241,14 @@
         <v>74</v>
       </c>
       <c r="F53" s="2" t="n">
+        <v>50500</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1847,6 +2275,14 @@
         <v>70</v>
       </c>
       <c r="F54" s="2" t="n">
+        <v>50501</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1873,6 +2309,14 @@
         <v>42</v>
       </c>
       <c r="F55" s="2" t="n">
+        <v>50502</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1899,6 +2343,14 @@
         <v>44</v>
       </c>
       <c r="F56" s="2" t="n">
+        <v>50590</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1925,6 +2377,14 @@
         <v>42</v>
       </c>
       <c r="F57" s="2" t="n">
+        <v>50591</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1951,6 +2411,14 @@
         <v>39</v>
       </c>
       <c r="F58" s="2" t="n">
+        <v>50592</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>GSM900</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
         <v>240</v>
       </c>
     </row>

--- a/network_excel_transformer/output/2G3G4G_Cell Info_CELLS_2G.xlsx
+++ b/network_excel_transformer/output/2G3G4G_Cell Info_CELLS_2G.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -545,7 +545,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -647,7 +647,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
@@ -715,7 +715,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -749,7 +749,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -783,7 +783,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -953,7 +953,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
@@ -987,7 +987,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>GSM900</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
